--- a/game_config/Datas/ItemConfig.xlsx
+++ b/game_config/Datas/ItemConfig.xlsx
@@ -1,60 +1,182 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A9F4C2-68F2-46EE-931F-34A94B4A9A66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ItemConfig" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ItemConfig" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>max_stack</t>
+  </si>
+  <si>
+    <t>use_effect</t>
+  </si>
+  <si>
+    <t>use_params</t>
+  </si>
+  <si>
+    <t>icon</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>(list#sep=,),int</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c,s</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>配置ID</t>
+  </si>
+  <si>
+    <t>显示名称</t>
+  </si>
+  <si>
+    <t>客户端描述</t>
+  </si>
+  <si>
+    <t>最大堆叠数量</t>
+  </si>
+  <si>
+    <t>使用效果：0不可用，1添加Buff，2执行Action</t>
+  </si>
+  <si>
+    <t>使用参数：按效果读取整数列表</t>
+  </si>
+  <si>
+    <t>客户端资源键；相对assets/resources，不含扩展名</t>
+  </si>
+  <si>
+    <t>小型生命药水</t>
+  </si>
+  <si>
+    <t>恢复少量生命值</t>
+  </si>
+  <si>
+    <t>UI/Icons/Items/1001</t>
+  </si>
+  <si>
+    <t>大型生命药水</t>
+  </si>
+  <si>
+    <t>恢复大量生命值</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>UI/Icons/Items/1002</t>
+  </si>
+  <si>
+    <t>1,150</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
-    <font/>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
+        <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
+        <fgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,93 +192,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -444,193 +509,172 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col min="1" max="3" width="12" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14" style="2" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="6"/>
+    <col min="8" max="8" width="38" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>max_stack</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>restore_hp</t>
-        </is>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>##group</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>配置ID</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>显示名称</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>客户端描述</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>最大堆叠数量</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>使用后恢复生命值</t>
-        </is>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="n">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="2">
         <v>1001</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>小型生命药水</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>恢复少量生命值</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
+      <c r="C5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="2">
         <v>99</v>
       </c>
-      <c r="F5" t="n">
-        <v>50</v>
+      <c r="F5" s="2">
+        <v>2</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" t="n">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="2">
         <v>1002</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>大型生命药水</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>恢复大量生命值</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
+      <c r="C6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="2">
         <v>99</v>
       </c>
-      <c r="F6" t="n">
-        <v>200</v>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/game_config/Datas/ItemConfig.xlsx
+++ b/game_config/Datas/ItemConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A9F4C2-68F2-46EE-931F-34A94B4A9A66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100169F8-D4C4-47A0-A762-988E895417F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,7 +117,7 @@
     <t>UI/Icons/Items/1002</t>
   </si>
   <si>
-    <t>1,150</t>
+    <t>6,150</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>

--- a/game_config/Datas/ItemConfig.xlsx
+++ b/game_config/Datas/ItemConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100169F8-D4C4-47A0-A762-988E895417F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F18920-9D7D-427C-B525-95FBC912F54E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemConfig" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -119,6 +119,18 @@
   <si>
     <t>6,150</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>cooldown_ms</t>
+  </si>
+  <si>
+    <t>global_cooldown_ms</t>
+  </si>
+  <si>
+    <t>道具自身冷却（毫秒）</t>
+  </si>
+  <si>
+    <t>与技能共享的公共冷却（毫秒）</t>
   </si>
 </sst>
 </file>
@@ -510,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="12" style="2" customWidth="1"/>
@@ -519,10 +531,12 @@
     <col min="6" max="6" width="14" style="2" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" style="6"/>
     <col min="8" max="8" width="38" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="2"/>
+    <col min="9" max="9" width="18.77734375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="24.77734375" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -547,8 +561,14 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -573,8 +593,14 @@
       <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="I2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
@@ -599,8 +625,14 @@
       <c r="H3" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
@@ -625,8 +657,14 @@
       <c r="H4" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="I4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>1001</v>
       </c>
@@ -648,8 +686,14 @@
       <c r="H5" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="I5" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="2">
         <v>1002</v>
       </c>
@@ -670,6 +714,12 @@
       </c>
       <c r="H6" s="2" t="s">
         <v>29</v>
+      </c>
+      <c r="I6" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/game_config/Datas/ItemConfig.xlsx
+++ b/game_config/Datas/ItemConfig.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -118,7 +118,6 @@
   </si>
   <si>
     <t>6,150</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>cooldown_ms</t>
@@ -131,6 +130,12 @@
   </si>
   <si>
     <t>与技能共享的公共冷却（毫秒）</t>
+  </si>
+  <si>
+    <t>任务怪物徽记</t>
+  </si>
+  <si>
+    <t>击败任务怪物后从尸体拾取</t>
   </si>
 </sst>
 </file>
@@ -522,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="12" style="2" customWidth="1"/>
@@ -722,6 +727,29 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="2">
+        <v>1101</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="2">
+        <v>99</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/game_config/Datas/ItemConfig.xlsx
+++ b/game_config/Datas/ItemConfig.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -136,6 +136,33 @@
   </si>
   <si>
     <t>击败任务怪物后从尸体拾取</t>
+  </si>
+  <si>
+    <t>buy_price</t>
+  </si>
+  <si>
+    <t>sell_price</t>
+  </si>
+  <si>
+    <t>NPC购买价格（金币）</t>
+  </si>
+  <si>
+    <t>NPC出售价格（金币）</t>
+  </si>
+  <si>
+    <t>破旧布料</t>
+  </si>
+  <si>
+    <t>怪物掉落的杂物，可卖给杂货商</t>
+  </si>
+  <si>
+    <t>小型法力药水</t>
+  </si>
+  <si>
+    <t>恢复少量法力值</t>
+  </si>
+  <si>
+    <t>1,2,150</t>
   </si>
 </sst>
 </file>
@@ -526,9 +553,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultRowHeight="14.4" ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="12" style="2" customWidth="1"/>
     <col min="4" max="4" width="15" style="2" customWidth="1"/>
@@ -541,7 +568,7 @@
     <col min="11" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -572,8 +599,14 @@
       <c r="J1" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -604,8 +637,14 @@
       <c r="J2" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
@@ -636,8 +675,14 @@
       <c r="J3" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="K3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
@@ -668,8 +713,14 @@
       <c r="J4" s="2" t="s">
         <v>34</v>
       </c>
+      <c r="K4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>1001</v>
       </c>
@@ -697,8 +748,14 @@
       <c r="J5" s="2">
         <v>1000</v>
       </c>
+      <c r="K5" s="2">
+        <v>50</v>
+      </c>
+      <c r="L5" s="2">
+        <v>20</v>
+      </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ac:dyDescent="0.25">
       <c r="B6" s="2">
         <v>1002</v>
       </c>
@@ -726,8 +783,14 @@
       <c r="J6" s="2">
         <v>1000</v>
       </c>
+      <c r="K6" s="2">
+        <v>100</v>
+      </c>
+      <c r="L6" s="2">
+        <v>50</v>
+      </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ac:dyDescent="0.25">
       <c r="B7" s="2">
         <v>1101</v>
       </c>
@@ -748,11 +811,78 @@
       </c>
       <c r="J7" s="2">
         <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ac:dyDescent="0.25">
+      <c r="B8" s="2">
+        <v>1201</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="2">
+        <v>99</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ac:dyDescent="0.25">
+      <c r="B9" s="2">
+        <v>1003</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="2">
+        <v>99</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K9" s="2">
+        <v>50</v>
+      </c>
+      <c r="L9" s="2">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" ns4:id="rId1"/>
 </worksheet>
 </file>
--- a/game_config/Datas/ItemConfig.xlsx
+++ b/game_config/Datas/ItemConfig.xlsx
@@ -553,9 +553,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultRowHeight="14.4" ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="12" style="2" customWidth="1"/>
     <col min="4" max="4" width="15" style="2" customWidth="1"/>
@@ -568,7 +568,7 @@
     <col min="11" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -606,7 +606,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -644,7 +644,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
@@ -682,7 +682,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
@@ -720,7 +720,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>1001</v>
       </c>
@@ -755,7 +755,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B6" s="2">
         <v>1002</v>
       </c>
@@ -790,7 +790,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B7" s="2">
         <v>1101</v>
       </c>
@@ -819,7 +819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
         <v>1201</v>
       </c>
@@ -848,7 +848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
         <v>1003</v>
       </c>
@@ -883,6 +883,6 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" ns4:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>